--- a/files/Sales Team - S1, S2 , CB, GB, South.xlsx
+++ b/files/Sales Team - S1, S2 , CB, GB, South.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://goapl-my.sharepoint.com/personal/anjani_parab_goapl_com/Documents/Desktop/FY Year -25-26/OPF SALES Abbreviation - FY25-26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="175" documentId="8_{A63597B2-0C8A-4124-96E2-B527C2816295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEADBA04-99B3-4DCA-AF20-44550E99D2E3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3986FDE-6D51-4267-86AD-57566FE56236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13000" xr2:uid="{008AE650-166D-4065-A85B-49D4E57142A2}"/>
   </bookViews>

--- a/files/Sales Team - S1, S2 , CB, GB, South.xlsx
+++ b/files/Sales Team - S1, S2 , CB, GB, South.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://goapl-my.sharepoint.com/personal/anjani_parab_goapl_com/Documents/Desktop/FY Year -25-26/OPF SALES Abbreviation - FY25-26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3986FDE-6D51-4267-86AD-57566FE56236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="175" documentId="8_{A63597B2-0C8A-4124-96E2-B527C2816295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEADBA04-99B3-4DCA-AF20-44550E99D2E3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13000" xr2:uid="{008AE650-166D-4065-A85B-49D4E57142A2}"/>
   </bookViews>
